--- a/templates/eml_metadata_template.xlsx
+++ b/templates/eml_metadata_template.xlsx
@@ -7,12 +7,15 @@
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="creators" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="personnel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="associated_parties" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -77,21 +80,18 @@
     <t xml:space="preserve">e.g. AU</t>
   </si>
   <si>
-    <t xml:space="preserve">Creator - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creator - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creator - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creator - email</t>
+    <t xml:space="preserve">Phone number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional - shared by everyone listed, like the address</t>
   </si>
   <si>
     <t xml:space="preserve">Metadata provider same as creator?</t>
   </si>
   <si>
+    <t xml:space="preserve">"Creator" here means the FIRST row of the separate 'creators' sheet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Metadata provider - given name</t>
   </si>
   <si>
@@ -122,30 +122,6 @@
     <t xml:space="preserve">Contact - email</t>
   </si>
   <si>
-    <t xml:space="preserve">Include an associated party?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - given name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if included</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - surname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Associated party - role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUBLISHER / AUTHOR / PROCESSOR / EDITOR / REVIEWER / OWNER</t>
-  </si>
-  <si>
     <t xml:space="preserve">Method steps</t>
   </si>
   <si>
@@ -215,16 +191,7 @@
     <t xml:space="preserve">org_country</t>
   </si>
   <si>
-    <t xml:space="preserve">creator_given</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creator_sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creator_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creator_email</t>
+    <t xml:space="preserve">org_phone</t>
   </si>
   <si>
     <t xml:space="preserve">mp_same</t>
@@ -257,24 +224,6 @@
     <t xml:space="preserve">contact_email</t>
   </si>
   <si>
-    <t xml:space="preserve">ap_include</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_given</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_sur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ap_role</t>
-  </si>
-  <si>
     <t xml:space="preserve">methods</t>
   </si>
   <si>
@@ -300,6 +249,27 @@
   </si>
   <si>
     <t xml:space="preserve">design_desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Given name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
   </si>
 </sst>
 </file>
@@ -665,7 +635,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -679,7 +649,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -693,7 +663,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -707,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -721,7 +691,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +705,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -749,7 +719,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -763,7 +733,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -777,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -791,7 +761,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
@@ -805,7 +775,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +789,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -830,43 +800,43 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>4</v>
@@ -875,12 +845,12 @@
         <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>4</v>
@@ -889,54 +859,54 @@
         <v>4</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>4</v>
@@ -945,12 +915,12 @@
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>4</v>
@@ -959,40 +929,40 @@
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>4</v>
@@ -1001,12 +971,12 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>4</v>
@@ -1015,40 +985,40 @@
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>4</v>
@@ -1057,12 +1027,12 @@
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>4</v>
@@ -1071,12 +1041,12 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>4</v>
@@ -1085,147 +1055,212 @@
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>51</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C38" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
-        <v>95</v>
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="22.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="14.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="16.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="28.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
